--- a/curation/draft/crf/CRF_VS.xlsx
+++ b/curation/draft/crf/CRF_VS.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\_github\cdisc-org\COSMoS\curation\draft\crf\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EB1463E-6398-41D1-A777-ED4ADD760A73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2BBC556-9744-48A6-8C0C-11E621F350CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2492,7 +2492,7 @@
     <row r="15" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A15" s="4"/>
       <c r="B15" t="s">
-        <v>43</v>
+        <v>77</v>
       </c>
       <c r="C15" t="s">
         <v>78</v>
@@ -4058,7 +4058,7 @@
     <row r="39" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A39" s="4"/>
       <c r="B39" t="s">
-        <v>137</v>
+        <v>119</v>
       </c>
       <c r="C39" t="s">
         <v>120</v>
@@ -5197,7 +5197,7 @@
     <row r="56" spans="1:35" ht="30" x14ac:dyDescent="0.25">
       <c r="A56" s="4"/>
       <c r="B56" t="s">
-        <v>156</v>
+        <v>137</v>
       </c>
       <c r="C56" t="s">
         <v>138</v>
@@ -5255,7 +5255,7 @@
     <row r="57" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A57" s="4"/>
       <c r="B57" t="s">
-        <v>156</v>
+        <v>137</v>
       </c>
       <c r="C57" t="s">
         <v>138</v>

--- a/curation/draft/crf/CRF_VS.xlsx
+++ b/curation/draft/crf/CRF_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\_github\cdisc-org\COSMoS\curation\draft\crf\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2BBC556-9744-48A6-8C0C-11E621F350CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93E5E8F6-F891-48CA-9F9E-89096E2ACF7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2528,7 +2528,7 @@
         <v>2</v>
       </c>
       <c r="T15" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="U15" t="s">
         <v>36</v>
@@ -2907,7 +2907,7 @@
         <v>2</v>
       </c>
       <c r="T21" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="U21" t="s">
         <v>36</v>
@@ -3561,7 +3561,7 @@
         <v>2</v>
       </c>
       <c r="T31" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="U31" t="s">
         <v>36</v>
@@ -4426,7 +4426,7 @@
         <v>2</v>
       </c>
       <c r="T44" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="U44" t="s">
         <v>36</v>
@@ -5291,7 +5291,7 @@
         <v>2</v>
       </c>
       <c r="T57" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="U57" t="s">
         <v>36</v>
@@ -5943,7 +5943,7 @@
         <v>2</v>
       </c>
       <c r="T67" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="U67" t="s">
         <v>36</v>
@@ -6786,7 +6786,7 @@
         <v>2</v>
       </c>
       <c r="T80" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="U80" t="s">
         <v>36</v>
@@ -7301,7 +7301,7 @@
         <v>2</v>
       </c>
       <c r="T88" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="U88" t="s">
         <v>36</v>
@@ -7814,7 +7814,7 @@
         <v>2</v>
       </c>
       <c r="T96" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="U96" t="s">
         <v>36</v>
@@ -8191,7 +8191,7 @@
         <v>3</v>
       </c>
       <c r="T102" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="U102" t="s">
         <v>36</v>
@@ -8640,7 +8640,7 @@
         <v>3</v>
       </c>
       <c r="T109" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="U109" t="s">
         <v>36</v>
